--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124192913</v>
+        <v>124191699</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410095</v>
+        <v>410171</v>
       </c>
       <c r="R13" t="n">
-        <v>6701528</v>
+        <v>6701395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124193734</v>
+        <v>124190554</v>
       </c>
       <c r="B14" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R14" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124190554</v>
+        <v>124192913</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410171</v>
+        <v>410095</v>
       </c>
       <c r="R15" t="n">
-        <v>6701395</v>
+        <v>6701528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124191699</v>
+        <v>124193734</v>
       </c>
       <c r="B17" t="n">
         <v>79428</v>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410171</v>
+        <v>409987</v>
       </c>
       <c r="R17" t="n">
-        <v>6701395</v>
+        <v>6701363</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124230024</v>
+        <v>124233006</v>
       </c>
       <c r="B18" t="n">
-        <v>80763</v>
+        <v>78455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,21 +2444,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410109</v>
+        <v>409927</v>
       </c>
       <c r="R18" t="n">
-        <v>6701358</v>
+        <v>6701367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124231394</v>
+        <v>124232353</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410055</v>
+        <v>409890</v>
       </c>
       <c r="R19" t="n">
-        <v>6701334</v>
+        <v>6701289</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124233006</v>
+        <v>124229574</v>
       </c>
       <c r="B20" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409927</v>
+        <v>410109</v>
       </c>
       <c r="R20" t="n">
-        <v>6701367</v>
+        <v>6701358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124229574</v>
+        <v>124231452</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,25 +2746,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R21" t="n">
-        <v>6701358</v>
+        <v>6701334</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124232353</v>
+        <v>124230024</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>80763</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409890</v>
+        <v>410109</v>
       </c>
       <c r="R22" t="n">
-        <v>6701289</v>
+        <v>6701358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124231452</v>
+        <v>124232165</v>
       </c>
       <c r="B24" t="n">
-        <v>79920</v>
+        <v>96354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R24" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124232245</v>
+        <v>124231394</v>
       </c>
       <c r="B25" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409907</v>
+        <v>410055</v>
       </c>
       <c r="R25" t="n">
-        <v>6701308</v>
+        <v>6701334</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124232165</v>
+        <v>124232245</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
+        <v>79851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124191699</v>
+        <v>124194211</v>
       </c>
       <c r="B13" t="n">
         <v>79428</v>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410171</v>
+        <v>409871</v>
       </c>
       <c r="R13" t="n">
-        <v>6701395</v>
+        <v>6701373</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124190554</v>
+        <v>124192913</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410171</v>
+        <v>410095</v>
       </c>
       <c r="R14" t="n">
-        <v>6701395</v>
+        <v>6701528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124192913</v>
+        <v>124191699</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410095</v>
+        <v>410171</v>
       </c>
       <c r="R15" t="n">
-        <v>6701528</v>
+        <v>6701395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124194211</v>
+        <v>124193734</v>
       </c>
       <c r="B16" t="n">
         <v>79428</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409871</v>
+        <v>409987</v>
       </c>
       <c r="R16" t="n">
-        <v>6701373</v>
+        <v>6701363</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124193734</v>
+        <v>124190554</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R17" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124233006</v>
+        <v>124232245</v>
       </c>
       <c r="B18" t="n">
-        <v>78455</v>
+        <v>79851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,25 +2440,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409927</v>
+        <v>409907</v>
       </c>
       <c r="R18" t="n">
-        <v>6701367</v>
+        <v>6701308</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124232353</v>
+        <v>124231730</v>
       </c>
       <c r="B19" t="n">
-        <v>96354</v>
+        <v>79851</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2542,25 +2542,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409890</v>
+        <v>410055</v>
       </c>
       <c r="R19" t="n">
-        <v>6701289</v>
+        <v>6701334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124229574</v>
+        <v>124233006</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78455</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410109</v>
+        <v>409927</v>
       </c>
       <c r="R20" t="n">
-        <v>6701358</v>
+        <v>6701367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124231452</v>
+        <v>124229574</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,25 +2746,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410055</v>
+        <v>410109</v>
       </c>
       <c r="R21" t="n">
-        <v>6701334</v>
+        <v>6701358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124230024</v>
+        <v>124231394</v>
       </c>
       <c r="B22" t="n">
-        <v>80763</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R22" t="n">
-        <v>6701358</v>
+        <v>6701334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124231730</v>
+        <v>124231452</v>
       </c>
       <c r="B23" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2954,21 +2954,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124232165</v>
+        <v>124230024</v>
       </c>
       <c r="B24" t="n">
-        <v>96354</v>
+        <v>80763</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409907</v>
+        <v>410109</v>
       </c>
       <c r="R24" t="n">
-        <v>6701308</v>
+        <v>6701358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124231394</v>
+        <v>124232165</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3158,21 +3158,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R25" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124232245</v>
+        <v>124232353</v>
       </c>
       <c r="B26" t="n">
-        <v>79851</v>
+        <v>96354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409907</v>
+        <v>409890</v>
       </c>
       <c r="R26" t="n">
-        <v>6701308</v>
+        <v>6701289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124191609</v>
+        <v>124191699</v>
       </c>
       <c r="B12" t="n">
-        <v>80763</v>
+        <v>79428</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,21 +1832,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124194211</v>
+        <v>124192913</v>
       </c>
       <c r="B13" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409871</v>
+        <v>410095</v>
       </c>
       <c r="R13" t="n">
-        <v>6701373</v>
+        <v>6701528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124192913</v>
+        <v>124190554</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410095</v>
+        <v>410171</v>
       </c>
       <c r="R14" t="n">
-        <v>6701528</v>
+        <v>6701395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,7 +2122,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124191699</v>
+        <v>124194211</v>
       </c>
       <c r="B15" t="n">
         <v>79428</v>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410171</v>
+        <v>409871</v>
       </c>
       <c r="R15" t="n">
-        <v>6701395</v>
+        <v>6701373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124193734</v>
+        <v>124191609</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>80763</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R16" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124190554</v>
+        <v>124193734</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410171</v>
+        <v>409987</v>
       </c>
       <c r="R17" t="n">
-        <v>6701395</v>
+        <v>6701363</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124232245</v>
+        <v>124233006</v>
       </c>
       <c r="B18" t="n">
-        <v>79851</v>
+        <v>78455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,25 +2440,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409907</v>
+        <v>409927</v>
       </c>
       <c r="R18" t="n">
-        <v>6701308</v>
+        <v>6701367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124233006</v>
+        <v>124232353</v>
       </c>
       <c r="B20" t="n">
-        <v>78455</v>
+        <v>96354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409927</v>
+        <v>409890</v>
       </c>
       <c r="R20" t="n">
-        <v>6701367</v>
+        <v>6701289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124229574</v>
+        <v>124230024</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124231394</v>
+        <v>124232165</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R22" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124231452</v>
+        <v>124231394</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2950,25 +2950,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124230024</v>
+        <v>124232245</v>
       </c>
       <c r="B24" t="n">
-        <v>80763</v>
+        <v>79851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410109</v>
+        <v>409907</v>
       </c>
       <c r="R24" t="n">
-        <v>6701358</v>
+        <v>6701308</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124232165</v>
+        <v>124231452</v>
       </c>
       <c r="B25" t="n">
-        <v>96354</v>
+        <v>79920</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409907</v>
+        <v>410055</v>
       </c>
       <c r="R25" t="n">
-        <v>6701308</v>
+        <v>6701334</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124232353</v>
+        <v>124229574</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409890</v>
+        <v>410109</v>
       </c>
       <c r="R26" t="n">
-        <v>6701289</v>
+        <v>6701358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124191699</v>
+        <v>124191609</v>
       </c>
       <c r="B12" t="n">
-        <v>79428</v>
+        <v>80763</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,21 +1832,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124190554</v>
+        <v>124193734</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410171</v>
+        <v>409987</v>
       </c>
       <c r="R14" t="n">
-        <v>6701395</v>
+        <v>6701363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124191609</v>
+        <v>124191699</v>
       </c>
       <c r="B16" t="n">
-        <v>80763</v>
+        <v>79428</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124193734</v>
+        <v>124190554</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R17" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124233006</v>
+        <v>124232165</v>
       </c>
       <c r="B18" t="n">
-        <v>78455</v>
+        <v>96354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,21 +2444,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409927</v>
+        <v>409907</v>
       </c>
       <c r="R18" t="n">
-        <v>6701367</v>
+        <v>6701308</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124231730</v>
+        <v>124231452</v>
       </c>
       <c r="B19" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124232353</v>
+        <v>124233006</v>
       </c>
       <c r="B20" t="n">
-        <v>96354</v>
+        <v>78455</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409890</v>
+        <v>409927</v>
       </c>
       <c r="R20" t="n">
-        <v>6701289</v>
+        <v>6701367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124230024</v>
+        <v>124232245</v>
       </c>
       <c r="B21" t="n">
-        <v>80763</v>
+        <v>79851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,25 +2746,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1049</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410109</v>
+        <v>409907</v>
       </c>
       <c r="R21" t="n">
-        <v>6701358</v>
+        <v>6701308</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124232165</v>
+        <v>124230024</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>80763</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409907</v>
+        <v>410109</v>
       </c>
       <c r="R22" t="n">
-        <v>6701308</v>
+        <v>6701358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124232245</v>
+        <v>124229574</v>
       </c>
       <c r="B24" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409907</v>
+        <v>410109</v>
       </c>
       <c r="R24" t="n">
-        <v>6701308</v>
+        <v>6701358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124231452</v>
+        <v>124232353</v>
       </c>
       <c r="B25" t="n">
-        <v>79920</v>
+        <v>96354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410055</v>
+        <v>409890</v>
       </c>
       <c r="R25" t="n">
-        <v>6701334</v>
+        <v>6701289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124229574</v>
+        <v>124231730</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>79851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R26" t="n">
-        <v>6701358</v>
+        <v>6701334</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124232353</v>
+        <v>124231730</v>
       </c>
       <c r="B25" t="n">
-        <v>96354</v>
+        <v>79851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409890</v>
+        <v>410055</v>
       </c>
       <c r="R25" t="n">
-        <v>6701289</v>
+        <v>6701334</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124231730</v>
+        <v>124232353</v>
       </c>
       <c r="B26" t="n">
-        <v>79851</v>
+        <v>96354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410055</v>
+        <v>409890</v>
       </c>
       <c r="R26" t="n">
-        <v>6701334</v>
+        <v>6701289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124192913</v>
+        <v>124191699</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410095</v>
+        <v>410171</v>
       </c>
       <c r="R13" t="n">
-        <v>6701528</v>
+        <v>6701395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124194211</v>
+        <v>124190554</v>
       </c>
       <c r="B15" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409871</v>
+        <v>410171</v>
       </c>
       <c r="R15" t="n">
-        <v>6701373</v>
+        <v>6701395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124191699</v>
+        <v>124194211</v>
       </c>
       <c r="B16" t="n">
         <v>79428</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410171</v>
+        <v>409871</v>
       </c>
       <c r="R16" t="n">
-        <v>6701395</v>
+        <v>6701373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124190554</v>
+        <v>124192913</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410171</v>
+        <v>410095</v>
       </c>
       <c r="R17" t="n">
-        <v>6701395</v>
+        <v>6701528</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124232165</v>
+        <v>124233006</v>
       </c>
       <c r="B18" t="n">
-        <v>96354</v>
+        <v>78455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2444,21 +2444,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409907</v>
+        <v>409927</v>
       </c>
       <c r="R18" t="n">
-        <v>6701308</v>
+        <v>6701367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124231452</v>
+        <v>124232165</v>
       </c>
       <c r="B19" t="n">
-        <v>79920</v>
+        <v>96354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2542,25 +2542,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R19" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124233006</v>
+        <v>124229574</v>
       </c>
       <c r="B20" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409927</v>
+        <v>410109</v>
       </c>
       <c r="R20" t="n">
-        <v>6701367</v>
+        <v>6701358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124230024</v>
+        <v>124232353</v>
       </c>
       <c r="B22" t="n">
-        <v>80763</v>
+        <v>96354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410109</v>
+        <v>409890</v>
       </c>
       <c r="R22" t="n">
-        <v>6701358</v>
+        <v>6701289</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124231394</v>
+        <v>124231452</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2950,25 +2950,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124229574</v>
+        <v>124231394</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R24" t="n">
-        <v>6701358</v>
+        <v>6701334</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124231730</v>
+        <v>124230024</v>
       </c>
       <c r="B25" t="n">
-        <v>79851</v>
+        <v>80763</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410055</v>
+        <v>410109</v>
       </c>
       <c r="R25" t="n">
-        <v>6701334</v>
+        <v>6701358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124232353</v>
+        <v>124231730</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
+        <v>79851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409890</v>
+        <v>410055</v>
       </c>
       <c r="R26" t="n">
-        <v>6701289</v>
+        <v>6701334</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124191609</v>
+        <v>124193734</v>
       </c>
       <c r="B12" t="n">
-        <v>80763</v>
+        <v>79428</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,21 +1832,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410171</v>
+        <v>409987</v>
       </c>
       <c r="R12" t="n">
-        <v>6701395</v>
+        <v>6701363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124191699</v>
+        <v>124191609</v>
       </c>
       <c r="B13" t="n">
-        <v>79428</v>
+        <v>80763</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124193734</v>
+        <v>124194211</v>
       </c>
       <c r="B14" t="n">
         <v>79428</v>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409987</v>
+        <v>409871</v>
       </c>
       <c r="R14" t="n">
-        <v>6701363</v>
+        <v>6701373</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124194211</v>
+        <v>124191699</v>
       </c>
       <c r="B16" t="n">
         <v>79428</v>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409871</v>
+        <v>410171</v>
       </c>
       <c r="R16" t="n">
-        <v>6701373</v>
+        <v>6701395</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124233006</v>
+        <v>124232245</v>
       </c>
       <c r="B18" t="n">
-        <v>78455</v>
+        <v>79851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,25 +2440,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409927</v>
+        <v>409907</v>
       </c>
       <c r="R18" t="n">
-        <v>6701367</v>
+        <v>6701308</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124232165</v>
+        <v>124231730</v>
       </c>
       <c r="B19" t="n">
-        <v>96354</v>
+        <v>79851</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2542,25 +2542,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409907</v>
+        <v>410055</v>
       </c>
       <c r="R19" t="n">
-        <v>6701308</v>
+        <v>6701334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124229574</v>
+        <v>124232165</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410109</v>
+        <v>409907</v>
       </c>
       <c r="R20" t="n">
-        <v>6701358</v>
+        <v>6701308</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124232245</v>
+        <v>124233006</v>
       </c>
       <c r="B21" t="n">
-        <v>79851</v>
+        <v>78455</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,25 +2746,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409907</v>
+        <v>409927</v>
       </c>
       <c r="R21" t="n">
-        <v>6701308</v>
+        <v>6701367</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124232353</v>
+        <v>124231452</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2848,25 +2848,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409890</v>
+        <v>410055</v>
       </c>
       <c r="R22" t="n">
-        <v>6701289</v>
+        <v>6701334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124231452</v>
+        <v>124229574</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2950,25 +2950,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410055</v>
+        <v>410109</v>
       </c>
       <c r="R23" t="n">
-        <v>6701334</v>
+        <v>6701358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124231394</v>
+        <v>124230024</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>80763</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410055</v>
+        <v>410109</v>
       </c>
       <c r="R24" t="n">
-        <v>6701334</v>
+        <v>6701358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124230024</v>
+        <v>124231394</v>
       </c>
       <c r="B25" t="n">
-        <v>80763</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3158,21 +3158,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R25" t="n">
-        <v>6701358</v>
+        <v>6701334</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124231730</v>
+        <v>124232353</v>
       </c>
       <c r="B26" t="n">
-        <v>79851</v>
+        <v>96354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3256,25 +3256,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410055</v>
+        <v>409890</v>
       </c>
       <c r="R26" t="n">
-        <v>6701334</v>
+        <v>6701289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124193734</v>
+        <v>124191699</v>
       </c>
       <c r="B12" t="n">
         <v>79428</v>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R12" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124194211</v>
+        <v>124190554</v>
       </c>
       <c r="B14" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409871</v>
+        <v>410171</v>
       </c>
       <c r="R14" t="n">
-        <v>6701373</v>
+        <v>6701395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124190554</v>
+        <v>124194211</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410171</v>
+        <v>409871</v>
       </c>
       <c r="R15" t="n">
-        <v>6701395</v>
+        <v>6701373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124191699</v>
+        <v>124192913</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410171</v>
+        <v>410095</v>
       </c>
       <c r="R16" t="n">
-        <v>6701395</v>
+        <v>6701528</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124192913</v>
+        <v>124193734</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410095</v>
+        <v>409987</v>
       </c>
       <c r="R17" t="n">
-        <v>6701528</v>
+        <v>6701363</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124232245</v>
+        <v>124233006</v>
       </c>
       <c r="B18" t="n">
-        <v>79851</v>
+        <v>78455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,25 +2440,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409907</v>
+        <v>409927</v>
       </c>
       <c r="R18" t="n">
-        <v>6701308</v>
+        <v>6701367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124231730</v>
+        <v>124231394</v>
       </c>
       <c r="B19" t="n">
-        <v>79851</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2542,25 +2542,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124232165</v>
+        <v>124230024</v>
       </c>
       <c r="B20" t="n">
-        <v>96354</v>
+        <v>80763</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409907</v>
+        <v>410109</v>
       </c>
       <c r="R20" t="n">
-        <v>6701308</v>
+        <v>6701358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124233006</v>
+        <v>124231730</v>
       </c>
       <c r="B21" t="n">
-        <v>78455</v>
+        <v>79851</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,25 +2746,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409927</v>
+        <v>410055</v>
       </c>
       <c r="R21" t="n">
-        <v>6701367</v>
+        <v>6701334</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124231452</v>
+        <v>124232245</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>79851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R22" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124229574</v>
+        <v>124231452</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2950,25 +2950,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R23" t="n">
-        <v>6701358</v>
+        <v>6701334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124230024</v>
+        <v>124232353</v>
       </c>
       <c r="B24" t="n">
-        <v>80763</v>
+        <v>96354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3056,21 +3056,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410109</v>
+        <v>409890</v>
       </c>
       <c r="R24" t="n">
-        <v>6701358</v>
+        <v>6701289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124231394</v>
+        <v>124232165</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3158,21 +3158,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R25" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124232353</v>
+        <v>124229574</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409890</v>
+        <v>410109</v>
       </c>
       <c r="R26" t="n">
-        <v>6701289</v>
+        <v>6701358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124191699</v>
+        <v>124190554</v>
       </c>
       <c r="B12" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,21 +1832,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124191609</v>
+        <v>124193734</v>
       </c>
       <c r="B13" t="n">
-        <v>80763</v>
+        <v>79428</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410171</v>
+        <v>409987</v>
       </c>
       <c r="R13" t="n">
-        <v>6701395</v>
+        <v>6701363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124190554</v>
+        <v>124194211</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,21 +2036,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410171</v>
+        <v>409871</v>
       </c>
       <c r="R14" t="n">
-        <v>6701395</v>
+        <v>6701373</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124194211</v>
+        <v>124191609</v>
       </c>
       <c r="B15" t="n">
-        <v>79428</v>
+        <v>80763</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409871</v>
+        <v>410171</v>
       </c>
       <c r="R15" t="n">
-        <v>6701373</v>
+        <v>6701395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2326,7 +2326,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124193734</v>
+        <v>124191699</v>
       </c>
       <c r="B17" t="n">
         <v>79428</v>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R17" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124231394</v>
+        <v>124230024</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>80763</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410055</v>
+        <v>410109</v>
       </c>
       <c r="R19" t="n">
-        <v>6701334</v>
+        <v>6701358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124230024</v>
+        <v>124229574</v>
       </c>
       <c r="B20" t="n">
-        <v>80763</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124231730</v>
+        <v>124231452</v>
       </c>
       <c r="B21" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124232245</v>
+        <v>124231730</v>
       </c>
       <c r="B22" t="n">
         <v>79851</v>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409907</v>
+        <v>410055</v>
       </c>
       <c r="R22" t="n">
-        <v>6701308</v>
+        <v>6701334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124231452</v>
+        <v>124232165</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
+        <v>96354</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2950,25 +2950,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R23" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124232353</v>
+        <v>124232245</v>
       </c>
       <c r="B24" t="n">
-        <v>96354</v>
+        <v>79851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409890</v>
+        <v>409907</v>
       </c>
       <c r="R24" t="n">
-        <v>6701289</v>
+        <v>6701308</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124232165</v>
+        <v>124232353</v>
       </c>
       <c r="B25" t="n">
         <v>96354</v>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409907</v>
+        <v>409890</v>
       </c>
       <c r="R25" t="n">
-        <v>6701308</v>
+        <v>6701289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124229574</v>
+        <v>124231394</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R26" t="n">
-        <v>6701358</v>
+        <v>6701334</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1816,10 +1816,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124190554</v>
+        <v>124193734</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,21 +1832,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410171</v>
+        <v>409987</v>
       </c>
       <c r="R12" t="n">
-        <v>6701395</v>
+        <v>6701363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124193734</v>
+        <v>124190554</v>
       </c>
       <c r="B13" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R13" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124232245</v>
+        <v>124232353</v>
       </c>
       <c r="B24" t="n">
-        <v>79851</v>
+        <v>96354</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409907</v>
+        <v>409890</v>
       </c>
       <c r="R24" t="n">
-        <v>6701308</v>
+        <v>6701289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124232353</v>
+        <v>124232245</v>
       </c>
       <c r="B25" t="n">
-        <v>96354</v>
+        <v>79851</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409890</v>
+        <v>409907</v>
       </c>
       <c r="R25" t="n">
-        <v>6701289</v>
+        <v>6701308</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -1816,7 +1816,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124193734</v>
+        <v>124191699</v>
       </c>
       <c r="B12" t="n">
         <v>79428</v>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409987</v>
+        <v>410171</v>
       </c>
       <c r="R12" t="n">
-        <v>6701363</v>
+        <v>6701395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124190554</v>
+        <v>124192913</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410171</v>
+        <v>410095</v>
       </c>
       <c r="R13" t="n">
-        <v>6701395</v>
+        <v>6701528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124194211</v>
+        <v>124193734</v>
       </c>
       <c r="B14" t="n">
         <v>79428</v>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409871</v>
+        <v>409987</v>
       </c>
       <c r="R14" t="n">
-        <v>6701373</v>
+        <v>6701363</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2122,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124191609</v>
+        <v>124190554</v>
       </c>
       <c r="B15" t="n">
-        <v>80763</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,21 +2138,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124192913</v>
+        <v>124194211</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>79428</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,21 +2240,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410095</v>
+        <v>409871</v>
       </c>
       <c r="R16" t="n">
-        <v>6701528</v>
+        <v>6701373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,10 +2326,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124191699</v>
+        <v>124191609</v>
       </c>
       <c r="B17" t="n">
-        <v>79428</v>
+        <v>80763</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,21 +2342,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124233006</v>
+        <v>124231730</v>
       </c>
       <c r="B18" t="n">
-        <v>78455</v>
+        <v>79851</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,25 +2440,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409927</v>
+        <v>410055</v>
       </c>
       <c r="R18" t="n">
-        <v>6701367</v>
+        <v>6701334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124230024</v>
+        <v>124233006</v>
       </c>
       <c r="B19" t="n">
-        <v>80763</v>
+        <v>78455</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410109</v>
+        <v>409927</v>
       </c>
       <c r="R19" t="n">
-        <v>6701358</v>
+        <v>6701367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124229574</v>
+        <v>124230024</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>80763</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124231452</v>
+        <v>124231394</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,25 +2746,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124231730</v>
+        <v>124231452</v>
       </c>
       <c r="B22" t="n">
-        <v>79851</v>
+        <v>79920</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,21 +2852,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124232165</v>
+        <v>124229574</v>
       </c>
       <c r="B23" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2954,21 +2954,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409907</v>
+        <v>410109</v>
       </c>
       <c r="R23" t="n">
-        <v>6701308</v>
+        <v>6701358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3040,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124232353</v>
+        <v>124232245</v>
       </c>
       <c r="B24" t="n">
-        <v>96354</v>
+        <v>79851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3052,25 +3052,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409890</v>
+        <v>409907</v>
       </c>
       <c r="R24" t="n">
-        <v>6701289</v>
+        <v>6701308</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124232245</v>
+        <v>124232353</v>
       </c>
       <c r="B25" t="n">
-        <v>79851</v>
+        <v>96354</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3154,25 +3154,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409907</v>
+        <v>409890</v>
       </c>
       <c r="R25" t="n">
-        <v>6701308</v>
+        <v>6701289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,10 +3244,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124231394</v>
+        <v>124232165</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3260,21 +3260,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R26" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -2632,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124230024</v>
+        <v>124229574</v>
       </c>
       <c r="B20" t="n">
-        <v>80763</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124231394</v>
+        <v>124232165</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>96354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410055</v>
+        <v>409907</v>
       </c>
       <c r="R21" t="n">
-        <v>6701334</v>
+        <v>6701308</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124231452</v>
+        <v>124231394</v>
       </c>
       <c r="B22" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2848,25 +2848,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2938,10 +2938,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124229574</v>
+        <v>124231452</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2950,25 +2950,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R23" t="n">
-        <v>6701358</v>
+        <v>6701334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124232353</v>
+        <v>124230024</v>
       </c>
       <c r="B25" t="n">
-        <v>96354</v>
+        <v>80763</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3158,21 +3158,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409890</v>
+        <v>410109</v>
       </c>
       <c r="R25" t="n">
-        <v>6701289</v>
+        <v>6701358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124232165</v>
+        <v>124232353</v>
       </c>
       <c r="B26" t="n">
         <v>96354</v>
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409907</v>
+        <v>409890</v>
       </c>
       <c r="R26" t="n">
-        <v>6701308</v>
+        <v>6701289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3344,6 +3344,730 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125337855</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80029</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>410092</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6701521</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125339785</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>410362</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6701601</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125337108</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79988</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>410028</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6701296</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125337097</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79894</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>388</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>410028</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6701294</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125337220</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91219</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>410028</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6701296</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125337110</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80063</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>410028</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6701296</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125337105</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80028</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>410028</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6701294</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3349,12 +3349,7 @@
         <v>125337855</v>
       </c>
       <c r="B27" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3448,15 +3443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125339785</v>
+        <v>125337097</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79936</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3464,39 +3454,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410362</v>
+        <v>410028</v>
       </c>
       <c r="R28" t="n">
-        <v>6701601</v>
+        <v>6701294</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,11 +3514,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,37 +3540,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337108</v>
+        <v>125337105</v>
       </c>
       <c r="B29" t="n">
-        <v>79988</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3603,7 +3578,7 @@
         <v>410028</v>
       </c>
       <c r="R29" t="n">
-        <v>6701296</v>
+        <v>6701294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3662,37 +3637,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337097</v>
+        <v>125337110</v>
       </c>
       <c r="B30" t="n">
-        <v>79894</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80105</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3705,7 +3675,7 @@
         <v>410028</v>
       </c>
       <c r="R30" t="n">
-        <v>6701294</v>
+        <v>6701296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3764,15 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337220</v>
+        <v>125337108</v>
       </c>
       <c r="B31" t="n">
-        <v>91219</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3780,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5321</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3866,50 +3831,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125337110</v>
+        <v>125339785</v>
       </c>
       <c r="B32" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410028</v>
+        <v>410362</v>
       </c>
       <c r="R32" t="n">
-        <v>6701296</v>
+        <v>6701601</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3942,6 +3907,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3968,37 +3938,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125337105</v>
+        <v>125337220</v>
       </c>
       <c r="B33" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4011,7 +3976,7 @@
         <v>410028</v>
       </c>
       <c r="R33" t="n">
-        <v>6701294</v>
+        <v>6701296</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3443,10 +3443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125337097</v>
+        <v>125337105</v>
       </c>
       <c r="B28" t="n">
-        <v>79936</v>
+        <v>80070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337105</v>
+        <v>125337097</v>
       </c>
       <c r="B29" t="n">
-        <v>80070</v>
+        <v>79936</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337110</v>
+        <v>125337108</v>
       </c>
       <c r="B30" t="n">
-        <v>80105</v>
+        <v>80030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337108</v>
+        <v>125337110</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>80105</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
         <v>125337220</v>
       </c>
       <c r="B33" t="n">
-        <v>91273</v>
+        <v>91280</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4033,6 +4033,782 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125997099</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>409876</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6701314</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125996810</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98331</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>409870</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6701239</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125996990</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91057</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6020</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Oljetagging</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sistotrema raduloides</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Donk</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>409870</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6701239</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125996629</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>409865</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6701219</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125997105</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80030</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>409874</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6701309</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125996620</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79936</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>388</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>409861</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6701218</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125996612</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79995</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6003719</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Traslav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Scytinium lichenoides</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>409865</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6701222</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125996642</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80030</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skavåsen, Skavåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>409862</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6701218</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4038,7 +4038,7 @@
         <v>125997099</v>
       </c>
       <c r="B34" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>125996990</v>
       </c>
       <c r="B36" t="n">
-        <v>91057</v>
+        <v>91058</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>125996629</v>
       </c>
       <c r="B37" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>125997105</v>
       </c>
       <c r="B38" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125996620</v>
       </c>
       <c r="B39" t="n">
-        <v>79936</v>
+        <v>79937</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>125996612</v>
       </c>
       <c r="B40" t="n">
-        <v>79995</v>
+        <v>79996</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>125996642</v>
       </c>
       <c r="B41" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3349,7 +3349,7 @@
         <v>125337855</v>
       </c>
       <c r="B27" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,10 +3443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125337105</v>
+        <v>125337097</v>
       </c>
       <c r="B28" t="n">
-        <v>80070</v>
+        <v>79937</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337097</v>
+        <v>125337105</v>
       </c>
       <c r="B29" t="n">
-        <v>79936</v>
+        <v>80071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337108</v>
+        <v>125337110</v>
       </c>
       <c r="B30" t="n">
-        <v>80030</v>
+        <v>80106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337110</v>
+        <v>125337108</v>
       </c>
       <c r="B31" t="n">
-        <v>80105</v>
+        <v>80031</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
         <v>125337220</v>
       </c>
       <c r="B33" t="n">
-        <v>91280</v>
+        <v>91281</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125996612</v>
+        <v>125996642</v>
       </c>
       <c r="B40" t="n">
-        <v>79996</v>
+        <v>80031</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,21 +4628,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409865</v>
+        <v>409862</v>
       </c>
       <c r="R40" t="n">
-        <v>6701222</v>
+        <v>6701218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125996642</v>
+        <v>125996612</v>
       </c>
       <c r="B41" t="n">
-        <v>80031</v>
+        <v>79996</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>6003719</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409862</v>
+        <v>409865</v>
       </c>
       <c r="R41" t="n">
-        <v>6701218</v>
+        <v>6701222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3349,7 +3349,7 @@
         <v>125337855</v>
       </c>
       <c r="B27" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>125337097</v>
       </c>
       <c r="B28" t="n">
-        <v>79937</v>
+        <v>79941</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>125337105</v>
       </c>
       <c r="B29" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337110</v>
+        <v>125337108</v>
       </c>
       <c r="B30" t="n">
-        <v>80106</v>
+        <v>80035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337108</v>
+        <v>125337110</v>
       </c>
       <c r="B31" t="n">
-        <v>80031</v>
+        <v>80110</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
         <v>125337220</v>
       </c>
       <c r="B33" t="n">
-        <v>91281</v>
+        <v>91285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>125997099</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>125996990</v>
       </c>
       <c r="B36" t="n">
-        <v>91058</v>
+        <v>91062</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>125996629</v>
       </c>
       <c r="B37" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>125997105</v>
       </c>
       <c r="B38" t="n">
-        <v>80031</v>
+        <v>80035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125996620</v>
       </c>
       <c r="B39" t="n">
-        <v>79937</v>
+        <v>79941</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125996642</v>
+        <v>125996612</v>
       </c>
       <c r="B40" t="n">
-        <v>80031</v>
+        <v>80000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,21 +4628,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6003719</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409862</v>
+        <v>409865</v>
       </c>
       <c r="R40" t="n">
-        <v>6701218</v>
+        <v>6701222</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125996612</v>
+        <v>125996642</v>
       </c>
       <c r="B41" t="n">
-        <v>79996</v>
+        <v>80035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409865</v>
+        <v>409862</v>
       </c>
       <c r="R41" t="n">
-        <v>6701222</v>
+        <v>6701218</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3443,10 +3443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125337097</v>
+        <v>125337105</v>
       </c>
       <c r="B28" t="n">
-        <v>79941</v>
+        <v>80075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337105</v>
+        <v>125337097</v>
       </c>
       <c r="B29" t="n">
-        <v>80075</v>
+        <v>79941</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337108</v>
+        <v>125337110</v>
       </c>
       <c r="B30" t="n">
-        <v>80035</v>
+        <v>80110</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337110</v>
+        <v>125337108</v>
       </c>
       <c r="B31" t="n">
-        <v>80110</v>
+        <v>80035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3443,10 +3443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125337105</v>
+        <v>125337097</v>
       </c>
       <c r="B28" t="n">
-        <v>80075</v>
+        <v>79941</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337097</v>
+        <v>125337105</v>
       </c>
       <c r="B29" t="n">
-        <v>79941</v>
+        <v>80075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3349,7 +3349,7 @@
         <v>125337855</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>125337097</v>
       </c>
       <c r="B28" t="n">
-        <v>79941</v>
+        <v>79942</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>125337105</v>
       </c>
       <c r="B29" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337110</v>
+        <v>125337108</v>
       </c>
       <c r="B30" t="n">
-        <v>80110</v>
+        <v>80036</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337108</v>
+        <v>125337110</v>
       </c>
       <c r="B31" t="n">
-        <v>80035</v>
+        <v>80111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3834,7 +3834,7 @@
         <v>125339785</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>125337220</v>
       </c>
       <c r="B33" t="n">
-        <v>91285</v>
+        <v>91287</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>125997099</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>125996990</v>
       </c>
       <c r="B36" t="n">
-        <v>91062</v>
+        <v>91064</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>125996629</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>125997105</v>
       </c>
       <c r="B38" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125996620</v>
       </c>
       <c r="B39" t="n">
-        <v>79941</v>
+        <v>79942</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125996612</v>
+        <v>125996642</v>
       </c>
       <c r="B40" t="n">
-        <v>80000</v>
+        <v>80036</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,21 +4628,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409865</v>
+        <v>409862</v>
       </c>
       <c r="R40" t="n">
-        <v>6701222</v>
+        <v>6701218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125996642</v>
+        <v>125996612</v>
       </c>
       <c r="B41" t="n">
-        <v>80035</v>
+        <v>80001</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>6003719</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409862</v>
+        <v>409865</v>
       </c>
       <c r="R41" t="n">
-        <v>6701218</v>
+        <v>6701222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3443,10 +3443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125337097</v>
+        <v>125337105</v>
       </c>
       <c r="B28" t="n">
-        <v>79942</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337105</v>
+        <v>125337097</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>79942</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
         <v>125337220</v>
       </c>
       <c r="B33" t="n">
-        <v>91287</v>
+        <v>91289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>125996990</v>
       </c>
       <c r="B36" t="n">
-        <v>91064</v>
+        <v>91066</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3637,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337108</v>
+        <v>125337110</v>
       </c>
       <c r="B30" t="n">
-        <v>80036</v>
+        <v>80111</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337110</v>
+        <v>125337108</v>
       </c>
       <c r="B31" t="n">
-        <v>80111</v>
+        <v>80036</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3941,7 +3941,7 @@
         <v>125337220</v>
       </c>
       <c r="B33" t="n">
-        <v>91289</v>
+        <v>91291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>125996990</v>
       </c>
       <c r="B36" t="n">
-        <v>91066</v>
+        <v>91068</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3349,7 +3349,7 @@
         <v>125337855</v>
       </c>
       <c r="B27" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3443,10 +3443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125337105</v>
+        <v>125337097</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337097</v>
+        <v>125337105</v>
       </c>
       <c r="B29" t="n">
-        <v>79942</v>
+        <v>80080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337110</v>
+        <v>125337108</v>
       </c>
       <c r="B30" t="n">
-        <v>80111</v>
+        <v>80040</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337108</v>
+        <v>125337110</v>
       </c>
       <c r="B31" t="n">
-        <v>80036</v>
+        <v>80115</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3834,7 +3834,7 @@
         <v>125339785</v>
       </c>
       <c r="B32" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>125337220</v>
       </c>
       <c r="B33" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>125997099</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>125996990</v>
       </c>
       <c r="B36" t="n">
-        <v>91068</v>
+        <v>91072</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>125996629</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>125997105</v>
       </c>
       <c r="B38" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125996620</v>
       </c>
       <c r="B39" t="n">
-        <v>79942</v>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>125996642</v>
       </c>
       <c r="B40" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>125996612</v>
       </c>
       <c r="B41" t="n">
-        <v>80001</v>
+        <v>80005</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3637,10 +3637,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337108</v>
+        <v>125337110</v>
       </c>
       <c r="B30" t="n">
-        <v>80040</v>
+        <v>80115</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337110</v>
+        <v>125337108</v>
       </c>
       <c r="B31" t="n">
-        <v>80115</v>
+        <v>80040</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -3443,10 +3443,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125337097</v>
+        <v>125337105</v>
       </c>
       <c r="B28" t="n">
-        <v>79946</v>
+        <v>80080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337105</v>
+        <v>125337097</v>
       </c>
       <c r="B29" t="n">
-        <v>80080</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4038,7 +4038,7 @@
         <v>125997099</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>125996990</v>
       </c>
       <c r="B36" t="n">
-        <v>91072</v>
+        <v>91075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>125996629</v>
       </c>
       <c r="B37" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>125997105</v>
       </c>
       <c r="B38" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>125996620</v>
       </c>
       <c r="B39" t="n">
-        <v>79946</v>
+        <v>79949</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>125996642</v>
       </c>
       <c r="B40" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>125996612</v>
       </c>
       <c r="B41" t="n">
-        <v>80005</v>
+        <v>80008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4617,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125996642</v>
+        <v>125996612</v>
       </c>
       <c r="B40" t="n">
-        <v>80043</v>
+        <v>80008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,21 +4628,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229497</v>
+        <v>6003719</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409862</v>
+        <v>409865</v>
       </c>
       <c r="R40" t="n">
-        <v>6701218</v>
+        <v>6701222</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125996612</v>
+        <v>125996642</v>
       </c>
       <c r="B41" t="n">
-        <v>80008</v>
+        <v>80043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409865</v>
+        <v>409862</v>
       </c>
       <c r="R41" t="n">
-        <v>6701222</v>
+        <v>6701218</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4617,10 +4617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125996612</v>
+        <v>125996642</v>
       </c>
       <c r="B40" t="n">
-        <v>80008</v>
+        <v>80043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,21 +4628,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409865</v>
+        <v>409862</v>
       </c>
       <c r="R40" t="n">
-        <v>6701222</v>
+        <v>6701218</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4714,10 +4714,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125996642</v>
+        <v>125996612</v>
       </c>
       <c r="B41" t="n">
-        <v>80043</v>
+        <v>80008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4725,21 +4725,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229497</v>
+        <v>6003719</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409862</v>
+        <v>409865</v>
       </c>
       <c r="R41" t="n">
-        <v>6701218</v>
+        <v>6701222</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4809,6 +4809,309 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129296544</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80010</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>388</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>409864</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6701212</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Känd lokal</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129296565</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80179</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>410013</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6701302</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129296543</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80010</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>388</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stiftgelélav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Collema furfuraceum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Arnold) Du Rietz</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>410021</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6701299</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B43" t="n">
-        <v>80179</v>
+        <v>80010</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R43" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4987,12 +4987,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5011,32 +5017,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B44" t="n">
-        <v>80010</v>
+        <v>80179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5046,10 +5052,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R44" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5084,18 +5090,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4814,7 +4814,7 @@
         <v>129296544</v>
       </c>
       <c r="B42" t="n">
-        <v>80010</v>
+        <v>80012</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>129296543</v>
       </c>
       <c r="B43" t="n">
-        <v>80010</v>
+        <v>80012</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>129296565</v>
       </c>
       <c r="B44" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B43" t="n">
-        <v>80012</v>
+        <v>80181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R43" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4987,18 +4987,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5017,32 +5011,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B44" t="n">
-        <v>80181</v>
+        <v>80012</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5052,10 +5046,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R44" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5090,12 +5084,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B43" t="n">
-        <v>80181</v>
+        <v>80012</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R43" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4987,12 +4987,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5011,32 +5017,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B44" t="n">
-        <v>80012</v>
+        <v>80181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5046,10 +5052,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R44" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5084,18 +5090,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4814,7 +4814,7 @@
         <v>129296544</v>
       </c>
       <c r="B42" t="n">
-        <v>80012</v>
+        <v>80014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B43" t="n">
-        <v>80181</v>
+        <v>80014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R43" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4987,12 +4987,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5011,32 +5017,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B44" t="n">
-        <v>80012</v>
+        <v>80183</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5046,10 +5052,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R44" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5084,18 +5090,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4814,7 +4814,7 @@
         <v>129296544</v>
       </c>
       <c r="B42" t="n">
-        <v>80014</v>
+        <v>80015</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>129296543</v>
       </c>
       <c r="B43" t="n">
-        <v>80014</v>
+        <v>80015</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>129296565</v>
       </c>
       <c r="B44" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B43" t="n">
-        <v>80015</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R43" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4987,18 +4987,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5017,32 +5011,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B44" t="n">
-        <v>80184</v>
+        <v>80015</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5052,10 +5046,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R44" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5090,12 +5084,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B43" t="n">
-        <v>80184</v>
+        <v>80015</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R43" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4987,12 +4987,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5011,32 +5017,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B44" t="n">
-        <v>80015</v>
+        <v>80184</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5046,10 +5052,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R44" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5084,18 +5090,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4811,7 +4811,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129296544</v>
+        <v>129296543</v>
       </c>
       <c r="B42" t="n">
         <v>80015</v>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409864</v>
+        <v>410021</v>
       </c>
       <c r="R42" t="n">
-        <v>6701212</v>
+        <v>6701299</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Känd lokal</t>
+          <t>Känd lokal, rotvälta asp</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4914,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B43" t="n">
-        <v>80015</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R43" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4987,18 +4987,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5014,103 +5008,6 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>129296565</v>
-      </c>
-      <c r="B44" t="n">
-        <v>80184</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Torsby kommun, Vrm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>410013</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6701302</v>
-      </c>
-      <c r="S44" t="n">
-        <v>15</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Norra Ny</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4811,32 +4811,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B42" t="n">
-        <v>80015</v>
+        <v>80184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R42" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4884,18 +4884,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4914,32 +4908,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B43" t="n">
-        <v>80184</v>
+        <v>80015</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4949,10 +4943,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R43" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4987,12 +4981,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4811,32 +4811,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B42" t="n">
-        <v>80184</v>
+        <v>80015</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R42" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4884,12 +4884,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4908,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B43" t="n">
-        <v>80015</v>
+        <v>80184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4943,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R43" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4981,18 +4987,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4811,32 +4811,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129296565</v>
+        <v>129296543</v>
       </c>
       <c r="B42" t="n">
-        <v>80184</v>
+        <v>80041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>388</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410013</v>
+        <v>410021</v>
       </c>
       <c r="R42" t="n">
-        <v>6701302</v>
+        <v>6701299</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4884,12 +4884,18 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4908,32 +4914,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296543</v>
+        <v>129296565</v>
       </c>
       <c r="B43" t="n">
-        <v>80015</v>
+        <v>80210</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>388</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4943,10 +4949,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410021</v>
+        <v>410013</v>
       </c>
       <c r="R43" t="n">
-        <v>6701299</v>
+        <v>6701302</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4981,18 +4987,12 @@
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4814,7 +4814,7 @@
         <v>129296543</v>
       </c>
       <c r="B42" t="n">
-        <v>80041</v>
+        <v>80046</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>129296565</v>
       </c>
       <c r="B43" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -4814,7 +4814,7 @@
         <v>129296543</v>
       </c>
       <c r="B42" t="n">
-        <v>80046</v>
+        <v>80047</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>129296565</v>
       </c>
       <c r="B43" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5009,6 +5009,129 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132312072</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57022</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>102935</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ejder</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Somateria mollissima</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Torsby kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>409864</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6701212</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5009,129 +5009,6 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>132312072</v>
-      </c>
-      <c r="B44" t="n">
-        <v>57022</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>102935</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Ejder</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Somateria mollissima</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Torsby kommun, Vrm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>409864</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6701212</v>
-      </c>
-      <c r="S44" t="n">
-        <v>15</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Torsby</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Norra Ny</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Joakim Karlsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97748891</v>
+        <v>123270756</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410055.2389834226</v>
+        <v>409943</v>
       </c>
       <c r="R2" t="n">
-        <v>6701496.893792032</v>
+        <v>6701304</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På stående gammal asp.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97748895</v>
+        <v>124232165</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410187.6452181179</v>
+        <v>409907</v>
       </c>
       <c r="R3" t="n">
-        <v>6701550.88872599</v>
+        <v>6701308</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,62 +871,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97748896</v>
+        <v>124232353</v>
       </c>
       <c r="B4" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410056.3622949368</v>
+        <v>409890</v>
       </c>
       <c r="R4" t="n">
-        <v>6701502.297565049</v>
+        <v>6701289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,27 +968,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97748887</v>
+        <v>123270751</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,37 +991,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409877.3770581844</v>
+        <v>409815</v>
       </c>
       <c r="R5" t="n">
-        <v>6701305.76739045</v>
+        <v>6701326</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,22 +1048,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,62 +1078,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97748886</v>
+        <v>124233006</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409911.6726887652</v>
+        <v>409927</v>
       </c>
       <c r="R6" t="n">
-        <v>6701292.569353289</v>
+        <v>6701367</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,22 +1155,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1175,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123270755</v>
+        <v>125337097</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,40 +1198,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409927</v>
+        <v>410028</v>
       </c>
       <c r="R7" t="n">
-        <v>6701337</v>
+        <v>6701294</v>
       </c>
       <c r="S7" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,22 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,27 +1272,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123270751</v>
+        <v>125996620</v>
       </c>
       <c r="B8" t="n">
-        <v>78433</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,40 +1295,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409815</v>
+        <v>409861</v>
       </c>
       <c r="R8" t="n">
-        <v>6701326</v>
+        <v>6701218</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,22 +1349,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,27 +1369,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123270756</v>
+        <v>129296543</v>
       </c>
       <c r="B9" t="n">
-        <v>96332</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,41 +1392,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>388</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409943</v>
+        <v>410021</v>
       </c>
       <c r="R9" t="n">
-        <v>6701304</v>
+        <v>6701299</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,22 +1446,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Känd lokal, rotvälta asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,33 +1465,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123266941</v>
+        <v>124191609</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,40 +1495,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409810</v>
+        <v>410171</v>
       </c>
       <c r="R10" t="n">
-        <v>6701318</v>
+        <v>6701395</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,22 +1549,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,27 +1569,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>martin eriksson</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123266817</v>
+        <v>124230024</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,40 +1592,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skavåsen, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409797</v>
+        <v>410109</v>
       </c>
       <c r="R11" t="n">
-        <v>6701306</v>
+        <v>6701358</v>
       </c>
       <c r="S11" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,22 +1646,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:32</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,15 +1678,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124191699</v>
+        <v>125337855</v>
       </c>
       <c r="B12" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1832,21 +1689,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1856,10 +1713,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410171</v>
+        <v>410092</v>
       </c>
       <c r="R12" t="n">
-        <v>6701395</v>
+        <v>6701521</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,12 +1743,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,49 +1763,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124192913</v>
+        <v>125337220</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1810,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410095</v>
+        <v>410028</v>
       </c>
       <c r="R13" t="n">
-        <v>6701528</v>
+        <v>6701296</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,12 +1840,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,27 +1860,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124193734</v>
+        <v>125996990</v>
       </c>
       <c r="B14" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,21 +1883,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6020</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409987</v>
+        <v>409870</v>
       </c>
       <c r="R14" t="n">
-        <v>6701363</v>
+        <v>6701239</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,12 +1937,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,31 +1957,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124190554</v>
+        <v>97748895</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2158,14 +2000,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>410171</v>
+        <v>410187</v>
       </c>
       <c r="R15" t="n">
-        <v>6701395</v>
+        <v>6701551</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2192,12 +2034,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2212,65 +2054,63 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124194211</v>
+        <v>123266817</v>
       </c>
       <c r="B16" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409871</v>
+        <v>409797</v>
       </c>
       <c r="R16" t="n">
-        <v>6701373</v>
+        <v>6701306</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2294,12 +2134,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2326,53 +2176,51 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124191609</v>
+        <v>123266941</v>
       </c>
       <c r="B17" t="n">
-        <v>80763</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410171</v>
+        <v>409810</v>
       </c>
       <c r="R17" t="n">
-        <v>6701395</v>
+        <v>6701318</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2396,12 +2244,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,65 +2274,63 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124231730</v>
+        <v>123270753</v>
       </c>
       <c r="B18" t="n">
-        <v>79851</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410055</v>
+        <v>409927</v>
       </c>
       <c r="R18" t="n">
-        <v>6701334</v>
+        <v>6701337</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2498,12 +2354,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2518,49 +2384,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>martin eriksson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124233006</v>
+        <v>124190554</v>
       </c>
       <c r="B19" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409927</v>
+        <v>410171</v>
       </c>
       <c r="R19" t="n">
-        <v>6701367</v>
+        <v>6701395</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,12 +2461,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,16 +2496,11 @@
         <v>124229574</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2734,15 +2590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124232165</v>
+        <v>124191699</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,21 +2601,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2625,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409907</v>
+        <v>410171</v>
       </c>
       <c r="R21" t="n">
-        <v>6701308</v>
+        <v>6701395</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,12 +2655,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2836,15 +2687,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124231394</v>
+        <v>124193734</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2852,21 +2698,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2876,10 +2722,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410055</v>
+        <v>409987</v>
       </c>
       <c r="R22" t="n">
-        <v>6701334</v>
+        <v>6701363</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,12 +2752,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2938,37 +2784,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124231452</v>
+        <v>124194211</v>
       </c>
       <c r="B23" t="n">
-        <v>79920</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2978,10 +2819,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410055</v>
+        <v>409871</v>
       </c>
       <c r="R23" t="n">
-        <v>6701334</v>
+        <v>6701373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3008,12 +2849,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3040,50 +2881,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124232245</v>
+        <v>97748887</v>
       </c>
       <c r="B24" t="n">
-        <v>79851</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409907</v>
+        <v>409878</v>
       </c>
       <c r="R24" t="n">
-        <v>6701308</v>
+        <v>6701306</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3110,12 +2946,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3130,27 +2966,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124230024</v>
+        <v>97748891</v>
       </c>
       <c r="B25" t="n">
-        <v>80763</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,34 +2989,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410109</v>
+        <v>410055</v>
       </c>
       <c r="R25" t="n">
-        <v>6701358</v>
+        <v>6701497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,12 +3043,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På stående gammal asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,27 +3068,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Johansson</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124232353</v>
+        <v>124192913</v>
       </c>
       <c r="B26" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3260,21 +3091,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3284,10 +3115,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409890</v>
+        <v>410095</v>
       </c>
       <c r="R26" t="n">
-        <v>6701289</v>
+        <v>6701528</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3314,12 +3145,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3346,10 +3177,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125337855</v>
+        <v>124231394</v>
       </c>
       <c r="B27" t="n">
-        <v>80081</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3357,21 +3188,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3381,10 +3212,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410092</v>
+        <v>410055</v>
       </c>
       <c r="R27" t="n">
-        <v>6701521</v>
+        <v>6701334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,12 +3242,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3431,12 +3262,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3446,7 +3277,7 @@
         <v>125337105</v>
       </c>
       <c r="B28" t="n">
-        <v>80080</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,10 +3371,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125337097</v>
+        <v>125996629</v>
       </c>
       <c r="B29" t="n">
-        <v>79946</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,21 +3382,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3575,10 +3406,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410028</v>
+        <v>409865</v>
       </c>
       <c r="R29" t="n">
-        <v>6701294</v>
+        <v>6701219</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,12 +3436,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3637,32 +3468,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125337110</v>
+        <v>125997099</v>
       </c>
       <c r="B30" t="n">
-        <v>80115</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,10 +3503,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410028</v>
+        <v>409876</v>
       </c>
       <c r="R30" t="n">
-        <v>6701296</v>
+        <v>6701314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3702,12 +3533,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3734,10 +3565,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125337108</v>
+        <v>124231452</v>
       </c>
       <c r="B31" t="n">
-        <v>80040</v>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3745,21 +3576,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,10 +3600,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>410028</v>
+        <v>410055</v>
       </c>
       <c r="R31" t="n">
-        <v>6701296</v>
+        <v>6701334</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3799,12 +3630,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3819,62 +3650,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125339785</v>
+        <v>125337110</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>410362</v>
+        <v>410028</v>
       </c>
       <c r="R32" t="n">
-        <v>6701601</v>
+        <v>6701296</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,11 +3733,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3938,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125337220</v>
+        <v>129296565</v>
       </c>
       <c r="B33" t="n">
-        <v>91295</v>
+        <v>80467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3949,37 +3770,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5321</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Torsby kommun, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>410028</v>
+        <v>410013</v>
       </c>
       <c r="R33" t="n">
-        <v>6701296</v>
+        <v>6701302</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4003,12 +3824,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4023,22 +3844,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Joakim Karlsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125997099</v>
+        <v>125339785</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4046,34 +3867,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409876</v>
+        <v>410362</v>
       </c>
       <c r="R34" t="n">
-        <v>6701314</v>
+        <v>6701601</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4100,12 +3926,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4135,7 +3966,7 @@
         <v>125996810</v>
       </c>
       <c r="B35" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4229,45 +4060,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125996990</v>
+        <v>97748886</v>
       </c>
       <c r="B36" t="n">
-        <v>91075</v>
+        <v>80392</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6020</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409870</v>
+        <v>409912</v>
       </c>
       <c r="R36" t="n">
-        <v>6701239</v>
+        <v>6701292</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4294,12 +4125,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4314,57 +4145,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125996629</v>
+        <v>97748896</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>80392</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skavåsen, Skavåsen, Vrm</t>
+          <t>Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409865</v>
+        <v>410056</v>
       </c>
       <c r="R37" t="n">
-        <v>6701219</v>
+        <v>6701502</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,12 +4222,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4411,22 +4242,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125997105</v>
+        <v>124231730</v>
       </c>
       <c r="B38" t="n">
-        <v>80043</v>
+        <v>80392</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,10 +4289,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409874</v>
+        <v>410055</v>
       </c>
       <c r="R38" t="n">
-        <v>6701309</v>
+        <v>6701334</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,12 +4319,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4508,44 +4339,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125996620</v>
+        <v>124232245</v>
       </c>
       <c r="B39" t="n">
-        <v>79949</v>
+        <v>80392</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>388</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4555,10 +4386,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409861</v>
+        <v>409907</v>
       </c>
       <c r="R39" t="n">
-        <v>6701218</v>
+        <v>6701308</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4585,12 +4416,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4605,22 +4436,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Linnea Johansson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125996612</v>
+        <v>125337108</v>
       </c>
       <c r="B40" t="n">
-        <v>80008</v>
+        <v>80392</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4628,21 +4459,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003719</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Traslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Scytinium lichenoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4652,10 +4483,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409865</v>
+        <v>410028</v>
       </c>
       <c r="R40" t="n">
-        <v>6701222</v>
+        <v>6701296</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4682,12 +4513,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4717,7 +4548,7 @@
         <v>125996642</v>
       </c>
       <c r="B41" t="n">
-        <v>80043</v>
+        <v>80392</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4811,48 +4642,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129296543</v>
+        <v>125997105</v>
       </c>
       <c r="B42" t="n">
-        <v>80047</v>
+        <v>80392</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>388</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>410021</v>
+        <v>409874</v>
       </c>
       <c r="R42" t="n">
-        <v>6701299</v>
+        <v>6701309</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4876,17 +4707,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Känd lokal, rotvälta asp</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4895,29 +4721,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129296565</v>
+        <v>125996612</v>
       </c>
       <c r="B43" t="n">
-        <v>80216</v>
+        <v>80357</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4925,37 +4750,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6003719</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Traslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scytinium lichenoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Torsby kommun, Vrm</t>
+          <t>Skavåsen, Skavåsen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>410013</v>
+        <v>409865</v>
       </c>
       <c r="R43" t="n">
-        <v>6701302</v>
+        <v>6701222</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4979,12 +4804,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4999,12 +4824,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joakim Karlsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 20818-2025 artfynd.xlsx
+++ b/artfynd/A 20818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123270756</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124232165</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124232353</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123270751</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124233006</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125337097</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1378,6 +1413,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125996620</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296543</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124191609</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124230024</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125337855</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1869,6 +1929,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125337220</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1966,6 +2031,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125996990</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2063,6 +2133,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748895</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2173,6 +2248,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123266817</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2283,6 +2363,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123266941</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123270753</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124190554</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2587,6 +2682,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124229574</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2684,6 +2784,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124191699</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2781,6 +2886,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124193734</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2878,6 +2988,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124194211</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2975,6 +3090,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748887</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3077,6 +3197,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748891</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3174,6 +3299,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124192913</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3271,6 +3401,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124231394</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3368,6 +3503,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125337105</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3465,6 +3605,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125996629</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3562,6 +3707,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125997099</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3659,6 +3809,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124231452</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3756,6 +3911,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125337110</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3853,6 +4013,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296565</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3960,6 +4125,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125339785</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4057,6 +4227,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125996810</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4154,6 +4329,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748886</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4251,6 +4431,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97748896</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4348,6 +4533,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124231730</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4445,6 +4635,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124232245</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4542,6 +4737,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125337108</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4639,6 +4839,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125996642</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4736,6 +4941,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125997105</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4833,8 +5043,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125996612</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>